--- a/PD Topics.xlsx
+++ b/PD Topics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\festi\Desktop\math-camp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90CCF0D-29CC-48F7-8DD4-395DFD632CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4431251-15BE-4381-BC7B-D04511A1EDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{D55A69C6-995B-4BDD-8F4D-FCAAA8935CD0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Zotero</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>Reading, journals, etc.</t>
+  </si>
+  <si>
+    <t>Options</t>
   </si>
 </sst>
 </file>
@@ -98,9 +101,10 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -123,9 +127,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -142,6 +153,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -468,29 +496,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B3" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B4" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B5" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="C5" s="1"/>
     </row>
@@ -498,49 +541,74 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B6" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B7" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B8" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B9" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B10" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="B11" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B12" s="2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="B13" s="2" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>